--- a/data/trans_dic/IQ2601_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IQ2601_R2-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46,85%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>70,38%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>78,58%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>69,5%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>57,23%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>58,8%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75,14%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>67,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,38%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,74; 77,07</t>
+          <t>59,22; 74,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,43; 66,28</t>
+          <t>38,48; 56,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,29; 67,01</t>
+          <t>62,2; 77,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60,32; 86,24</t>
+          <t>62,56; 90,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,94; 74,05</t>
+          <t>61,81; 76,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,59; 55,79</t>
+          <t>47,71; 65,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,32; 77,39</t>
+          <t>48,92; 67,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62,05; 89,63</t>
+          <t>59,89; 85,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,61; 73,74</t>
+          <t>63,2; 74,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,89; 58,42</t>
+          <t>46,11; 57,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59,0; 70,38</t>
+          <t>58,62; 71,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,35; 84,76</t>
+          <t>65,48; 85,16</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>73,3%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>77,84%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>76,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>67,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>68,38%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>73,3%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>53,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,95; 82,73</t>
+          <t>65,08; 80,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,73; 74,53</t>
+          <t>44,25; 61,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,0; 75,28</t>
+          <t>51,14; 66,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,88; 76,08</t>
+          <t>59,86; 89,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,08; 80,47</t>
+          <t>67,7; 82,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,97; 61,8</t>
+          <t>59,1; 75,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,95; 66,1</t>
+          <t>61,19; 75,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,61; 89,93</t>
+          <t>44,62; 76,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69,46; 79,82</t>
+          <t>69,05; 79,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,89; 65,61</t>
+          <t>54,0; 65,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58,39; 68,59</t>
+          <t>57,95; 68,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,44; 78,44</t>
+          <t>55,71; 78,5</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>62,19%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49,05%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71,76%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>48,37%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>65,35%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>48,89%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>55,79%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>60,7%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>62,19%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,91; 73,92</t>
+          <t>54,61; 69,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,73; 57,48</t>
+          <t>40,05; 58,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,24; 65,91</t>
+          <t>63,0; 79,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,4; 85,09</t>
+          <t>27,42; 69,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,33; 69,66</t>
+          <t>56,26; 74,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,65; 57,83</t>
+          <t>39,85; 58,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,39; 79,74</t>
+          <t>46,24; 65,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,46; 67,52</t>
+          <t>34,12; 82,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,63; 69,4</t>
+          <t>57,33; 69,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,5; 55,1</t>
+          <t>43,04; 55,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57,07; 70,81</t>
+          <t>56,97; 70,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,42; 67,76</t>
+          <t>36,41; 68,24</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65,76%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>75,7%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>70,28%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>49,73%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>64,09%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>79,43%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>62,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>65,76%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,66; 75,5</t>
+          <t>56,67; 68,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,39; 56,14</t>
+          <t>42,84; 54,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,16; 69,24</t>
+          <t>59,81; 70,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66,52; 89,29</t>
+          <t>62,39; 86,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,86; 67,77</t>
+          <t>65,36; 75,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,77; 53,46</t>
+          <t>44,73; 55,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,7; 70,62</t>
+          <t>59,12; 68,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,98; 87,0</t>
+          <t>64,15; 88,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,3; 69,95</t>
+          <t>62,3; 69,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,03; 53,22</t>
+          <t>44,77; 53,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61,03; 68,51</t>
+          <t>61,08; 68,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,35; 85,96</t>
+          <t>67,52; 84,49</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>64,66%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52,6%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>62,86%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77,88%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>69,29%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>50,09%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>64,88%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>83,42%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>64,66%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>52,6%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>62,86%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>62,37; 76,59</t>
+          <t>57,4; 70,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,17; 57,3</t>
+          <t>45,59; 59,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58,42; 71,14</t>
+          <t>55,25; 69,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68,28; 92,24</t>
+          <t>64,43; 86,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,79; 71,36</t>
+          <t>62,25; 76,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,86; 60,59</t>
+          <t>43,76; 56,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,45; 69,69</t>
+          <t>57,39; 70,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,84; 86,84</t>
+          <t>64,15; 91,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,52; 71,84</t>
+          <t>61,37; 71,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,27; 57,13</t>
+          <t>46,35; 55,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,01; 68,1</t>
+          <t>58,67; 68,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,25; 87,21</t>
+          <t>68,26; 85,62</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40,35%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>56,95%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73,16%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>47,75%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>46,68%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>62,66%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24,54%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>61,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,95%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,93; 57,71</t>
+          <t>51,92; 70,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,32; 58,64</t>
+          <t>31,45; 50,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52,76; 72,68</t>
+          <t>47,25; 67,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 47,46</t>
+          <t>54,04; 86,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,38; 70,29</t>
+          <t>37,86; 56,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,66; 51,01</t>
+          <t>35,59; 58,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,4; 66,65</t>
+          <t>51,34; 72,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56,79; 88,29</t>
+          <t>11,18; 49,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,67; 61,13</t>
+          <t>47,75; 61,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36,38; 50,18</t>
+          <t>36,45; 50,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51,99; 66,71</t>
+          <t>52,71; 66,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42,82; 71,42</t>
+          <t>38,21; 69,91</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49,02%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>64,51%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>74,21%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>67,57%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>52,83%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>63,37%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>69,38%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>64,71%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,51%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64,37; 70,73</t>
+          <t>61,84; 67,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,69; 56,15</t>
+          <t>46,05; 52,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60,63; 66,36</t>
+          <t>61,34; 67,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62,75; 75,88</t>
+          <t>67,87; 79,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>61,79; 67,81</t>
+          <t>64,64; 70,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,84; 52,39</t>
+          <t>49,22; 55,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,26; 67,31</t>
+          <t>60,33; 66,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,84; 79,18</t>
+          <t>60,45; 73,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>64,01; 68,12</t>
+          <t>64,07; 68,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,64; 52,99</t>
+          <t>48,54; 53,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61,87; 66,0</t>
+          <t>61,86; 66,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,84; 75,85</t>
+          <t>66,66; 75,56</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>63635</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39901</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>68380</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28907</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>70257</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>49585</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>47024</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22285</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>63635</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>39901</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>68380</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51693</t>
+          <t>50988</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>62408; 77905</t>
+          <t>56245; 70783</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41964; 57430</t>
+          <t>32773; 47991</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39416; 53591</t>
+          <t>60440; 75119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17891; 25578</t>
+          <t>23015; 33279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55985; 70330</t>
+          <t>62477; 77409</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32015; 47516</t>
+          <t>41338; 56577</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60551; 75193</t>
+          <t>39121; 53727</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23374; 33767</t>
+          <t>17826; 25498</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>122759; 144584</t>
+          <t>123916; 145263</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78843; 100374</t>
+          <t>79222; 99346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104509; 124666</t>
+          <t>103846; 126274</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44672; 57072</t>
+          <t>43577; 56675</t>
         </is>
       </c>
     </row>
@@ -2004,32 +2004,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>103</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63020</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49698</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>65627</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>64083</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>70589</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15010</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>63020</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49698</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65627</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>30684</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57256; 69711</t>
+          <t>55949; 69187</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52881; 67100</t>
+          <t>41305; 57293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62972; 77715</t>
+          <t>56970; 74144</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10932; 18529</t>
+          <t>11918; 17850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55949; 69176</t>
+          <t>57045; 69710</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41976; 57686</t>
+          <t>53206; 67546</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56758; 73638</t>
+          <t>63169; 77616</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12666; 19107</t>
+          <t>11099; 19102</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118247; 135876</t>
+          <t>117552; 136149</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98824; 120318</t>
+          <t>99035; 120751</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125336; 147220</t>
+          <t>124375; 147328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25738; 35771</t>
+          <t>24950; 35153</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>61276</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40636</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53176</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7852</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>43171</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>40459</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>34501</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7016</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>61276</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40636</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>53176</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>14984</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36936; 48829</t>
+          <t>53801; 68944</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32874; 47567</t>
+          <t>33175; 48267</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27977; 40758</t>
+          <t>46679; 58685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4092; 9835</t>
+          <t>4452; 11272</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>53524; 68629</t>
+          <t>37161; 49202</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32850; 47908</t>
+          <t>32979; 48567</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46233; 59087</t>
+          <t>28594; 40620</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4852; 11929</t>
+          <t>4043; 9746</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94841; 114216</t>
+          <t>94361; 114058</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>70379; 91238</t>
+          <t>71269; 91689</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77582; 96254</t>
+          <t>77450; 96180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10645; 19804</t>
+          <t>10224; 19164</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>122164</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106751</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137856</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32072</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>137885</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>99102</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>141067</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29815</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>122164</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>106751</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>137856</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35795</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65609</t>
+          <t>59936</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>126858; 148119</t>
+          <t>111331; 133970</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88462; 111863</t>
+          <t>94128; 118827</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130222; 152395</t>
+          <t>125375; 148045</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24969; 33518</t>
+          <t>26434; 36846</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>111693; 133119</t>
+          <t>128229; 147214</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93965; 117455</t>
+          <t>89137; 111234</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>125159; 148038</t>
+          <t>130123; 151564</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29418; 40640</t>
+          <t>22868; 31535</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>244595; 274658</t>
+          <t>244591; 274598</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>188652; 222984</t>
+          <t>187578; 222411</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>262287; 294390</t>
+          <t>262498; 293123</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>58428; 72419</t>
+          <t>52677; 65918</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>80543</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72942</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89326</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30760</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>70289</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>72240</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>87605</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19340</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>80543</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>72942</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89326</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32269</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51609</t>
+          <t>46717</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>63275; 77697</t>
+          <t>71506; 88382</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62259; 82648</t>
+          <t>63218; 81940</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78887; 96055</t>
+          <t>78516; 98936</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15830; 21385</t>
+          <t>25447; 34348</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>71989; 88883</t>
+          <t>63149; 77621</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63603; 84030</t>
+          <t>63115; 81928</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78799; 99032</t>
+          <t>77495; 95799</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27169; 36389</t>
+          <t>12792; 18181</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>139049; 162375</t>
+          <t>138703; 160836</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>130907; 161620</t>
+          <t>131131; 158212</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>163526; 188731</t>
+          <t>162579; 189307</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45723; 56760</t>
+          <t>40569; 50888</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>42936</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>28544</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>38628</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>15230</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>35386</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>24278</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>37904</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3194</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>42936</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>28544</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>38628</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>18892</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28107; 42761</t>
+          <t>36082; 49149</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18367; 30500</t>
+          <t>22246; 35712</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31917; 43967</t>
+          <t>32045; 45683</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1245; 6179</t>
+          <t>11248; 17931</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36405; 48851</t>
+          <t>28058; 42022</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21691; 36085</t>
+          <t>18509; 30236</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31468; 45208</t>
+          <t>31054; 43993</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13370; 20788</t>
+          <t>1527; 6718</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68450; 87784</t>
+          <t>68574; 88213</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44651; 61592</t>
+          <t>44742; 61962</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66716; 85600</t>
+          <t>67631; 85772</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15656; 26114</t>
+          <t>13174; 24102</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>504</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>433574</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>338472</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>452993</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>130318</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>421072</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>345990</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>418690</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>96662</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>433574</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>338472</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>452993</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>139675</t>
+          <t>91883</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>236337</t>
+          <t>222201</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>401145; 440723</t>
+          <t>414340; 454347</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>325428; 367735</t>
+          <t>317942; 361355</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>400547; 438447</t>
+          <t>430734; 472975</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87426; 105714</t>
+          <t>119184; 140087</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>413987; 454323</t>
+          <t>402812; 439299</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>316533; 361719</t>
+          <t>322338; 366134</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>430163; 472650</t>
+          <t>398556; 440165</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>128048; 149453</t>
+          <t>82044; 100357</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>827681; 880905</t>
+          <t>828557; 881807</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>654473; 712992</t>
+          <t>653085; 715027</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>843286; 899453</t>
+          <t>843066; 899937</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>222568; 248824</t>
+          <t>207546; 235247</t>
         </is>
       </c>
     </row>
